--- a/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -368,25 +368,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>sd_visits</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>q1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>median</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>q3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n_pts</t>
         </is>
@@ -400,18 +410,24 @@
         <v>3.06</v>
       </c>
       <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
         <v>2.39</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
       <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>4</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>18324</v>
       </c>
     </row>
@@ -423,18 +439,24 @@
         <v>2.64</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>25</v>
+      </c>
+      <c r="E3">
         <v>2.2</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
         <v>15007</v>
       </c>
     </row>
@@ -446,18 +468,24 @@
         <v>2.61</v>
       </c>
       <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>36</v>
+      </c>
+      <c r="E4">
         <v>2.17</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>13521</v>
       </c>
     </row>
@@ -469,18 +497,24 @@
         <v>2.48</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
         <v>2.05</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
         <v>12297</v>
       </c>
     </row>
@@ -492,18 +526,24 @@
         <v>2.48</v>
       </c>
       <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>34</v>
+      </c>
+      <c r="E6">
         <v>2.09</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
         <v>10837</v>
       </c>
     </row>
@@ -515,18 +555,24 @@
         <v>2.47</v>
       </c>
       <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>24</v>
+      </c>
+      <c r="E7">
         <v>2.05</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
         <v>10023</v>
       </c>
     </row>
@@ -538,18 +584,24 @@
         <v>2.47</v>
       </c>
       <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
         <v>2.04</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
         <v>9330</v>
       </c>
     </row>
@@ -561,18 +613,24 @@
         <v>2.4</v>
       </c>
       <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
         <v>1.98</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
       <c r="F9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
         <v>8918</v>
       </c>
     </row>
@@ -584,18 +642,24 @@
         <v>2.46</v>
       </c>
       <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>32</v>
+      </c>
+      <c r="E10">
         <v>2.03</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
         <v>8562</v>
       </c>
     </row>
@@ -607,18 +671,24 @@
         <v>2.39</v>
       </c>
       <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>34</v>
+      </c>
+      <c r="E11">
         <v>1.94</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
         <v>8181</v>
       </c>
     </row>
@@ -630,18 +700,24 @@
         <v>2.41</v>
       </c>
       <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>42</v>
+      </c>
+      <c r="E12">
         <v>1.99</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
         <v>7905</v>
       </c>
     </row>
@@ -653,18 +729,24 @@
         <v>2.45</v>
       </c>
       <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>32</v>
+      </c>
+      <c r="E13">
         <v>2.01</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
         <v>7693</v>
       </c>
     </row>
@@ -676,18 +758,24 @@
         <v>2.42</v>
       </c>
       <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14">
         <v>1.96</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
       <c r="F14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
         <v>7405</v>
       </c>
     </row>
@@ -699,18 +787,24 @@
         <v>2.42</v>
       </c>
       <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>21</v>
+      </c>
+      <c r="E15">
         <v>1.97</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15">
         <v>7053</v>
       </c>
     </row>
@@ -722,18 +816,24 @@
         <v>2.45</v>
       </c>
       <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>18</v>
+      </c>
+      <c r="E16">
         <v>1.98</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
       <c r="F16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
         <v>6818</v>
       </c>
     </row>
@@ -745,18 +845,24 @@
         <v>2.4</v>
       </c>
       <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>21</v>
+      </c>
+      <c r="E17">
         <v>1.95</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
       <c r="F17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
         <v>6550</v>
       </c>
     </row>
@@ -768,18 +874,24 @@
         <v>2.39</v>
       </c>
       <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>18</v>
+      </c>
+      <c r="E18">
         <v>1.86</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
       <c r="F18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18">
         <v>6392</v>
       </c>
     </row>
@@ -791,18 +903,24 @@
         <v>2.42</v>
       </c>
       <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>23</v>
+      </c>
+      <c r="E19">
         <v>2.02</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
       <c r="F19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
         <v>6156</v>
       </c>
     </row>
@@ -814,18 +932,24 @@
         <v>2.39</v>
       </c>
       <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>25</v>
+      </c>
+      <c r="E20">
         <v>1.96</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
       <c r="F20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20">
         <v>6001</v>
       </c>
     </row>
@@ -837,18 +961,24 @@
         <v>2.4</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
         <v>5751</v>
       </c>
     </row>
@@ -860,18 +990,24 @@
         <v>2.43</v>
       </c>
       <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="E22">
         <v>1.98</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
         <v>5651</v>
       </c>
     </row>
@@ -883,18 +1019,24 @@
         <v>2.37</v>
       </c>
       <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>21</v>
+      </c>
+      <c r="E23">
         <v>1.88</v>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
       <c r="F23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
         <v>5388</v>
       </c>
     </row>
@@ -906,18 +1048,24 @@
         <v>2.4</v>
       </c>
       <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>20</v>
+      </c>
+      <c r="E24">
         <v>1.94</v>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
       <c r="F24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
         <v>5228</v>
       </c>
     </row>
@@ -929,18 +1077,24 @@
         <v>2.42</v>
       </c>
       <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>19</v>
+      </c>
+      <c r="E25">
         <v>1.96</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
       <c r="F25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
         <v>4949</v>
       </c>
     </row>
@@ -952,18 +1106,24 @@
         <v>1.06</v>
       </c>
       <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
         <v>0.24</v>
       </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
         <v>157</v>
       </c>
     </row>
@@ -974,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -990,25 +1150,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>sd_visits</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>q1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>median</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>q3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n_pts</t>
         </is>
@@ -1022,18 +1192,24 @@
         <v>3.06</v>
       </c>
       <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
         <v>2.39</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
       <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>4</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>18324</v>
       </c>
     </row>
@@ -1045,18 +1221,24 @@
         <v>2.65</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>25</v>
+      </c>
+      <c r="E3">
         <v>2.21</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
         <v>14871</v>
       </c>
     </row>
@@ -1068,18 +1250,24 @@
         <v>2.61</v>
       </c>
       <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>36</v>
+      </c>
+      <c r="E4">
         <v>2.18</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>13417</v>
       </c>
     </row>
@@ -1091,18 +1279,24 @@
         <v>2.52</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
         <v>2.07</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
         <v>11768</v>
       </c>
     </row>
@@ -1114,18 +1308,24 @@
         <v>2.5</v>
       </c>
       <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>34</v>
+      </c>
+      <c r="E6">
         <v>2.1</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
         <v>10615</v>
       </c>
     </row>
@@ -1137,18 +1337,24 @@
         <v>2.48</v>
       </c>
       <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>24</v>
+      </c>
+      <c r="E7">
         <v>2.06</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
         <v>9848</v>
       </c>
     </row>
@@ -1160,18 +1366,24 @@
         <v>2.47</v>
       </c>
       <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
         <v>2.04</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
         <v>9231</v>
       </c>
     </row>
@@ -1183,18 +1395,24 @@
         <v>2.41</v>
       </c>
       <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
         <v>1.98</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
       <c r="F9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
         <v>8815</v>
       </c>
     </row>
@@ -1206,18 +1424,24 @@
         <v>2.46</v>
       </c>
       <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>32</v>
+      </c>
+      <c r="E10">
         <v>2.03</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
         <v>8481</v>
       </c>
     </row>
@@ -1229,18 +1453,24 @@
         <v>2.4</v>
       </c>
       <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>34</v>
+      </c>
+      <c r="E11">
         <v>1.94</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
         <v>8113</v>
       </c>
     </row>
@@ -1252,18 +1482,24 @@
         <v>2.42</v>
       </c>
       <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>42</v>
+      </c>
+      <c r="E12">
         <v>1.99</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
         <v>7841</v>
       </c>
     </row>
@@ -1275,18 +1511,24 @@
         <v>2.45</v>
       </c>
       <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>32</v>
+      </c>
+      <c r="E13">
         <v>2.02</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
         <v>7624</v>
       </c>
     </row>
@@ -1298,18 +1540,24 @@
         <v>2.42</v>
       </c>
       <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14">
         <v>1.97</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
       <c r="F14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
         <v>7351</v>
       </c>
     </row>
@@ -1321,18 +1569,24 @@
         <v>2.42</v>
       </c>
       <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>21</v>
+      </c>
+      <c r="E15">
         <v>1.97</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15">
         <v>7013</v>
       </c>
     </row>
@@ -1344,18 +1598,24 @@
         <v>2.45</v>
       </c>
       <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>18</v>
+      </c>
+      <c r="E16">
         <v>1.98</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
       <c r="F16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
         <v>6768</v>
       </c>
     </row>
@@ -1367,18 +1627,24 @@
         <v>2.41</v>
       </c>
       <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>21</v>
+      </c>
+      <c r="E17">
         <v>1.95</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
       <c r="F17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
         <v>6499</v>
       </c>
     </row>
@@ -1390,18 +1656,24 @@
         <v>2.39</v>
       </c>
       <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>18</v>
+      </c>
+      <c r="E18">
         <v>1.86</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
       <c r="F18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18">
         <v>6348</v>
       </c>
     </row>
@@ -1413,18 +1685,24 @@
         <v>2.42</v>
       </c>
       <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>23</v>
+      </c>
+      <c r="E19">
         <v>2.02</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
       <c r="F19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
         <v>6118</v>
       </c>
     </row>
@@ -1436,18 +1714,24 @@
         <v>2.4</v>
       </c>
       <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>25</v>
+      </c>
+      <c r="E20">
         <v>1.96</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
       <c r="F20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20">
         <v>5969</v>
       </c>
     </row>
@@ -1459,18 +1743,24 @@
         <v>2.4</v>
       </c>
       <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21">
         <v>1.99</v>
       </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
         <v>5720</v>
       </c>
     </row>
@@ -1482,18 +1772,24 @@
         <v>2.43</v>
       </c>
       <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="E22">
         <v>1.97</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
         <v>5616</v>
       </c>
     </row>
@@ -1505,18 +1801,24 @@
         <v>2.37</v>
       </c>
       <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>21</v>
+      </c>
+      <c r="E23">
         <v>1.89</v>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
       <c r="F23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
         <v>5352</v>
       </c>
     </row>
@@ -1528,18 +1830,24 @@
         <v>2.41</v>
       </c>
       <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>20</v>
+      </c>
+      <c r="E24">
         <v>1.95</v>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
       <c r="F24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
         <v>5205</v>
       </c>
     </row>
@@ -1551,18 +1859,24 @@
         <v>2.42</v>
       </c>
       <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>19</v>
+      </c>
+      <c r="E25">
         <v>1.97</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
       <c r="F25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
         <v>4920</v>
       </c>
     </row>
@@ -1574,18 +1888,24 @@
         <v>1</v>
       </c>
       <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
         <v>0</v>
       </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
         <v>6</v>
       </c>
     </row>

--- a/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -404,10 +404,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -416,7 +416,7 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -428,15 +428,15 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>18324</v>
+        <v>18397</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -445,7 +445,7 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -457,15 +457,15 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>15007</v>
+        <v>14899</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -474,7 +474,7 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -486,24 +486,24 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>13521</v>
+        <v>13603</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -515,15 +515,15 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>12297</v>
+        <v>12172</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -532,7 +532,7 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -544,15 +544,15 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>10837</v>
+        <v>10899</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -573,24 +573,24 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>10023</v>
+        <v>9958</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -602,15 +602,15 @@
         <v>3</v>
       </c>
       <c r="I8">
-        <v>9330</v>
+        <v>9390</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -619,7 +619,7 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -631,24 +631,24 @@
         <v>3</v>
       </c>
       <c r="I9">
-        <v>8918</v>
+        <v>8834</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -660,24 +660,24 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>8562</v>
+        <v>8539</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -689,24 +689,24 @@
         <v>3</v>
       </c>
       <c r="I11">
-        <v>8181</v>
+        <v>8229</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -718,24 +718,24 @@
         <v>3</v>
       </c>
       <c r="I12">
-        <v>7905</v>
+        <v>7828</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -747,24 +747,24 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>7693</v>
+        <v>7774</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -776,15 +776,15 @@
         <v>3</v>
       </c>
       <c r="I14">
-        <v>7405</v>
+        <v>7336</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -793,7 +793,7 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -805,15 +805,15 @@
         <v>3</v>
       </c>
       <c r="I15">
-        <v>7053</v>
+        <v>7102</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -834,24 +834,24 @@
         <v>3</v>
       </c>
       <c r="I16">
-        <v>6818</v>
+        <v>6745</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -863,15 +863,15 @@
         <v>3</v>
       </c>
       <c r="I17">
-        <v>6550</v>
+        <v>6597</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -892,24 +892,24 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>6392</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E19">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -921,15 +921,15 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>6156</v>
+        <v>6141</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -950,15 +950,15 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>6001</v>
+        <v>6024</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -967,7 +967,7 @@
         <v>20</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -979,15 +979,15 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>5751</v>
+        <v>5719</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -996,7 +996,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1008,15 +1008,15 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>5651</v>
+        <v>5703</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1037,15 +1037,15 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>5388</v>
+        <v>5333</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1066,15 +1066,15 @@
         <v>3</v>
       </c>
       <c r="I24">
-        <v>5228</v>
+        <v>5305</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1083,7 +1083,7 @@
         <v>19</v>
       </c>
       <c r="E25">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1095,36 +1095,7 @@
         <v>3</v>
       </c>
       <c r="I25">
-        <v>4949</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>1.06</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-      <c r="E26">
-        <v>0.24</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
-        <v>157</v>
+        <v>4859</v>
       </c>
     </row>
   </sheetData>
@@ -1134,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1186,10 +1157,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1198,7 +1169,7 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1210,15 +1181,15 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>18324</v>
+        <v>18397</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1227,7 +1198,7 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1239,15 +1210,15 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>14871</v>
+        <v>14586</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1256,7 +1227,7 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1268,24 +1239,24 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>13417</v>
+        <v>13322</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1297,15 +1268,15 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>11768</v>
+        <v>11204</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1314,7 +1285,7 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1326,15 +1297,15 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>10615</v>
+        <v>10401</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1343,7 +1314,7 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1355,24 +1326,24 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>9848</v>
+        <v>9636</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1384,15 +1355,15 @@
         <v>3</v>
       </c>
       <c r="I8">
-        <v>9231</v>
+        <v>9155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1401,7 +1372,7 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1413,24 +1384,24 @@
         <v>3</v>
       </c>
       <c r="I9">
-        <v>8815</v>
+        <v>8626</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1442,24 +1413,24 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>8481</v>
+        <v>8367</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1471,24 +1442,24 @@
         <v>3</v>
       </c>
       <c r="I11">
-        <v>8113</v>
+        <v>8071</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1500,24 +1471,24 @@
         <v>3</v>
       </c>
       <c r="I12">
-        <v>7841</v>
+        <v>7710</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1529,24 +1500,24 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>7624</v>
+        <v>7619</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1558,15 +1529,15 @@
         <v>3</v>
       </c>
       <c r="I14">
-        <v>7351</v>
+        <v>7222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1575,7 +1546,7 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1587,15 +1558,15 @@
         <v>3</v>
       </c>
       <c r="I15">
-        <v>7013</v>
+        <v>6998</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1616,12 +1587,12 @@
         <v>3</v>
       </c>
       <c r="I16">
-        <v>6768</v>
+        <v>6637</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>2.41</v>
@@ -1630,7 +1601,7 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17">
         <v>1.95</v>
@@ -1645,15 +1616,15 @@
         <v>3</v>
       </c>
       <c r="I17">
-        <v>6499</v>
+        <v>6492</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1674,24 +1645,24 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>6348</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E19">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1703,15 +1674,15 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>6118</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1720,7 +1691,7 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1732,15 +1703,15 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>5969</v>
+        <v>5952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1749,7 +1720,7 @@
         <v>20</v>
       </c>
       <c r="E21">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1761,15 +1732,15 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>5720</v>
+        <v>5642</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1778,7 +1749,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1790,15 +1761,15 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>5616</v>
+        <v>5622</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1807,7 +1778,7 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1819,15 +1790,15 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>5352</v>
+        <v>5258</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1836,7 +1807,7 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1848,65 +1819,7 @@
         <v>3</v>
       </c>
       <c r="I24">
-        <v>5205</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>2.42</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>19</v>
-      </c>
-      <c r="E25">
-        <v>1.97</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>2</v>
-      </c>
-      <c r="H25">
-        <v>3</v>
-      </c>
-      <c r="I25">
-        <v>4920</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
-        <v>6</v>
+        <v>5249</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
@@ -407,16 +407,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E2">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -428,7 +428,7 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>18397</v>
+        <v>18396</v>
       </c>
     </row>
     <row r="3">
@@ -436,16 +436,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -457,7 +457,7 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>14899</v>
+        <v>14967</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -474,7 +474,7 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -486,7 +486,7 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>13603</v>
+        <v>13635</v>
       </c>
     </row>
     <row r="5">
@@ -494,16 +494,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -515,7 +515,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>12172</v>
+        <v>12226</v>
       </c>
     </row>
     <row r="6">
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -532,7 +532,7 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -544,7 +544,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>10899</v>
+        <v>10968</v>
       </c>
     </row>
     <row r="7">
@@ -552,16 +552,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -573,7 +573,7 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>9958</v>
+        <v>10006</v>
       </c>
     </row>
     <row r="8">
@@ -581,16 +581,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -602,7 +602,7 @@
         <v>3</v>
       </c>
       <c r="I8">
-        <v>9390</v>
+        <v>9483</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -619,7 +619,7 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -631,7 +631,7 @@
         <v>3</v>
       </c>
       <c r="I9">
-        <v>8834</v>
+        <v>8950</v>
       </c>
     </row>
     <row r="10">
@@ -639,7 +639,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -648,7 +648,7 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>8539</v>
+        <v>8646</v>
       </c>
     </row>
     <row r="11">
@@ -668,7 +668,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -677,7 +677,7 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -689,7 +689,7 @@
         <v>3</v>
       </c>
       <c r="I11">
-        <v>8229</v>
+        <v>8306</v>
       </c>
     </row>
     <row r="12">
@@ -697,16 +697,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E12">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -718,7 +718,7 @@
         <v>3</v>
       </c>
       <c r="I12">
-        <v>7828</v>
+        <v>7877</v>
       </c>
     </row>
     <row r="13">
@@ -726,7 +726,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -735,7 +735,7 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -747,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>7774</v>
+        <v>7824</v>
       </c>
     </row>
     <row r="14">
@@ -755,7 +755,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -764,7 +764,7 @@
         <v>29</v>
       </c>
       <c r="E14">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -776,7 +776,7 @@
         <v>3</v>
       </c>
       <c r="I14">
-        <v>7336</v>
+        <v>7375</v>
       </c>
     </row>
     <row r="15">
@@ -784,7 +784,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -793,7 +793,7 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="I15">
-        <v>7102</v>
+        <v>7187</v>
       </c>
     </row>
     <row r="16">
@@ -813,16 +813,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>3</v>
       </c>
       <c r="I16">
-        <v>6745</v>
+        <v>6824</v>
       </c>
     </row>
     <row r="17">
@@ -842,16 +842,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -863,7 +863,7 @@
         <v>3</v>
       </c>
       <c r="I17">
-        <v>6597</v>
+        <v>6696</v>
       </c>
     </row>
     <row r="18">
@@ -871,7 +871,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="E18">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -892,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>6328</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="19">
@@ -900,16 +900,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E19">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -921,7 +921,7 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>6141</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="20">
@@ -929,7 +929,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -950,7 +950,7 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>6024</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="21">
@@ -958,7 +958,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -967,7 +967,7 @@
         <v>20</v>
       </c>
       <c r="E21">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>5719</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="22">
@@ -987,7 +987,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -996,7 +996,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1008,7 +1008,7 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>5703</v>
+        <v>5764</v>
       </c>
     </row>
     <row r="23">
@@ -1016,16 +1016,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E23">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1037,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>5333</v>
+        <v>5406</v>
       </c>
     </row>
     <row r="24">
@@ -1045,7 +1045,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1066,7 +1066,7 @@
         <v>3</v>
       </c>
       <c r="I24">
-        <v>5305</v>
+        <v>5358</v>
       </c>
     </row>
     <row r="25">
@@ -1074,16 +1074,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E25">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1095,7 +1095,7 @@
         <v>3</v>
       </c>
       <c r="I25">
-        <v>4859</v>
+        <v>4954</v>
       </c>
     </row>
   </sheetData>
@@ -1160,16 +1160,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E2">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1181,7 +1181,7 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>18397</v>
+        <v>18396</v>
       </c>
     </row>
     <row r="3">
@@ -1189,16 +1189,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1210,7 +1210,7 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>14586</v>
+        <v>14651</v>
       </c>
     </row>
     <row r="4">
@@ -1218,7 +1218,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1227,7 +1227,7 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1239,7 +1239,7 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>13322</v>
+        <v>13352</v>
       </c>
     </row>
     <row r="5">
@@ -1247,16 +1247,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1268,7 +1268,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>11204</v>
+        <v>11304</v>
       </c>
     </row>
     <row r="6">
@@ -1276,7 +1276,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1285,7 +1285,7 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>10401</v>
+        <v>10493</v>
       </c>
     </row>
     <row r="7">
@@ -1305,16 +1305,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1326,7 +1326,7 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>9636</v>
+        <v>9694</v>
       </c>
     </row>
     <row r="8">
@@ -1334,16 +1334,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1355,7 +1355,7 @@
         <v>3</v>
       </c>
       <c r="I8">
-        <v>9155</v>
+        <v>9248</v>
       </c>
     </row>
     <row r="9">
@@ -1363,7 +1363,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1372,7 +1372,7 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1384,7 +1384,7 @@
         <v>3</v>
       </c>
       <c r="I9">
-        <v>8626</v>
+        <v>8750</v>
       </c>
     </row>
     <row r="10">
@@ -1392,7 +1392,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1401,7 +1401,7 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1413,7 +1413,7 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>8367</v>
+        <v>8476</v>
       </c>
     </row>
     <row r="11">
@@ -1421,7 +1421,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1430,7 +1430,7 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1442,7 +1442,7 @@
         <v>3</v>
       </c>
       <c r="I11">
-        <v>8071</v>
+        <v>8152</v>
       </c>
     </row>
     <row r="12">
@@ -1450,16 +1450,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E12">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1471,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="I12">
-        <v>7710</v>
+        <v>7759</v>
       </c>
     </row>
     <row r="13">
@@ -1479,7 +1479,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1500,7 +1500,7 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>7619</v>
+        <v>7669</v>
       </c>
     </row>
     <row r="14">
@@ -1508,7 +1508,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1517,7 +1517,7 @@
         <v>29</v>
       </c>
       <c r="E14">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1529,7 +1529,7 @@
         <v>3</v>
       </c>
       <c r="I14">
-        <v>7222</v>
+        <v>7262</v>
       </c>
     </row>
     <row r="15">
@@ -1537,7 +1537,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1546,7 +1546,7 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1558,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="I15">
-        <v>6998</v>
+        <v>7081</v>
       </c>
     </row>
     <row r="16">
@@ -1566,16 +1566,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1587,7 +1587,7 @@
         <v>3</v>
       </c>
       <c r="I16">
-        <v>6637</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="17">
@@ -1595,16 +1595,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1616,7 +1616,7 @@
         <v>3</v>
       </c>
       <c r="I17">
-        <v>6492</v>
+        <v>6592</v>
       </c>
     </row>
     <row r="18">
@@ -1624,7 +1624,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1633,7 +1633,7 @@
         <v>18</v>
       </c>
       <c r="E18">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>6238</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="19">
@@ -1653,16 +1653,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1674,7 +1674,7 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>6050</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="20">
@@ -1682,7 +1682,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1691,7 +1691,7 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1703,7 +1703,7 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>5952</v>
+        <v>6028</v>
       </c>
     </row>
     <row r="21">
@@ -1711,7 +1711,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1720,7 +1720,7 @@
         <v>20</v>
       </c>
       <c r="E21">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>5642</v>
+        <v>5714</v>
       </c>
     </row>
     <row r="22">
@@ -1740,7 +1740,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1749,7 +1749,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1761,7 +1761,7 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>5622</v>
+        <v>5685</v>
       </c>
     </row>
     <row r="23">
@@ -1769,16 +1769,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E23">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1790,7 +1790,7 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>5258</v>
+        <v>5332</v>
       </c>
     </row>
     <row r="24">
@@ -1798,7 +1798,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1807,7 +1807,7 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1819,7 +1819,7 @@
         <v>3</v>
       </c>
       <c r="I24">
-        <v>5249</v>
+        <v>5303</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
@@ -407,7 +407,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -416,19 +416,19 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>4</v>
       </c>
       <c r="I2">
-        <v>18396</v>
+        <v>18925</v>
       </c>
     </row>
     <row r="3">
@@ -436,7 +436,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -445,7 +445,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -454,10 +454,10 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>14967</v>
+        <v>15445</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -474,7 +474,7 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -483,10 +483,10 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4">
-        <v>13635</v>
+        <v>14088</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -503,7 +503,7 @@
         <v>38</v>
       </c>
       <c r="E5">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -515,7 +515,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>12226</v>
+        <v>12614</v>
       </c>
     </row>
     <row r="6">
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -532,7 +532,7 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -544,7 +544,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>10968</v>
+        <v>11322</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +552,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -573,7 +573,7 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>10006</v>
+        <v>10363</v>
       </c>
     </row>
     <row r="8">
@@ -581,16 +581,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -602,7 +602,7 @@
         <v>3</v>
       </c>
       <c r="I8">
-        <v>9483</v>
+        <v>9780</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -619,7 +619,7 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -631,7 +631,7 @@
         <v>3</v>
       </c>
       <c r="I9">
-        <v>8950</v>
+        <v>9232</v>
       </c>
     </row>
     <row r="10">
@@ -639,7 +639,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -648,7 +648,7 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>8646</v>
+        <v>8898</v>
       </c>
     </row>
     <row r="11">
@@ -668,7 +668,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -677,7 +677,7 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -689,7 +689,7 @@
         <v>3</v>
       </c>
       <c r="I11">
-        <v>8306</v>
+        <v>8566</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +697,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -706,7 +706,7 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -718,7 +718,7 @@
         <v>3</v>
       </c>
       <c r="I12">
-        <v>7877</v>
+        <v>8131</v>
       </c>
     </row>
     <row r="13">
@@ -726,7 +726,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -735,7 +735,7 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -747,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>7824</v>
+        <v>8056</v>
       </c>
     </row>
     <row r="14">
@@ -755,7 +755,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -764,7 +764,7 @@
         <v>29</v>
       </c>
       <c r="E14">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -776,7 +776,7 @@
         <v>3</v>
       </c>
       <c r="I14">
-        <v>7375</v>
+        <v>7628</v>
       </c>
     </row>
     <row r="15">
@@ -784,7 +784,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -793,7 +793,7 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="I15">
-        <v>7187</v>
+        <v>7416</v>
       </c>
     </row>
     <row r="16">
@@ -813,16 +813,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E16">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>3</v>
       </c>
       <c r="I16">
-        <v>6824</v>
+        <v>7051</v>
       </c>
     </row>
     <row r="17">
@@ -842,7 +842,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -851,7 +851,7 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -863,7 +863,7 @@
         <v>3</v>
       </c>
       <c r="I17">
-        <v>6696</v>
+        <v>6913</v>
       </c>
     </row>
     <row r="18">
@@ -871,7 +871,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="E18">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -892,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>6390</v>
+        <v>6599</v>
       </c>
     </row>
     <row r="19">
@@ -900,7 +900,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -909,7 +909,7 @@
         <v>30</v>
       </c>
       <c r="E19">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -921,7 +921,7 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>6206</v>
+        <v>6429</v>
       </c>
     </row>
     <row r="20">
@@ -929,7 +929,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -950,7 +950,7 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>6099</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="21">
@@ -958,7 +958,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -967,7 +967,7 @@
         <v>20</v>
       </c>
       <c r="E21">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>5791</v>
+        <v>5955</v>
       </c>
     </row>
     <row r="22">
@@ -987,7 +987,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -996,7 +996,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1008,7 +1008,7 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>5764</v>
+        <v>5929</v>
       </c>
     </row>
     <row r="23">
@@ -1016,16 +1016,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1037,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>5406</v>
+        <v>5565</v>
       </c>
     </row>
     <row r="24">
@@ -1045,7 +1045,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1066,7 +1066,7 @@
         <v>3</v>
       </c>
       <c r="I24">
-        <v>5358</v>
+        <v>5525</v>
       </c>
     </row>
     <row r="25">
@@ -1074,7 +1074,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1083,7 +1083,7 @@
         <v>20</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1095,7 +1095,7 @@
         <v>3</v>
       </c>
       <c r="I25">
-        <v>4954</v>
+        <v>5110</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1169,19 +1169,19 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>4</v>
       </c>
       <c r="I2">
-        <v>18396</v>
+        <v>18925</v>
       </c>
     </row>
     <row r="3">
@@ -1189,7 +1189,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1198,7 +1198,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1207,10 +1207,10 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>14651</v>
+        <v>15122</v>
       </c>
     </row>
     <row r="4">
@@ -1218,7 +1218,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1227,7 +1227,7 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1236,10 +1236,10 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4">
-        <v>13352</v>
+        <v>13797</v>
       </c>
     </row>
     <row r="5">
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1256,7 +1256,7 @@
         <v>38</v>
       </c>
       <c r="E5">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1268,7 +1268,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>11304</v>
+        <v>11630</v>
       </c>
     </row>
     <row r="6">
@@ -1276,7 +1276,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1285,7 +1285,7 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>10493</v>
+        <v>10819</v>
       </c>
     </row>
     <row r="7">
@@ -1305,7 +1305,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1314,7 +1314,7 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1326,7 +1326,7 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>9694</v>
+        <v>10035</v>
       </c>
     </row>
     <row r="8">
@@ -1334,16 +1334,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1355,7 +1355,7 @@
         <v>3</v>
       </c>
       <c r="I8">
-        <v>9248</v>
+        <v>9539</v>
       </c>
     </row>
     <row r="9">
@@ -1363,7 +1363,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1372,7 +1372,7 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1384,7 +1384,7 @@
         <v>3</v>
       </c>
       <c r="I9">
-        <v>8750</v>
+        <v>9022</v>
       </c>
     </row>
     <row r="10">
@@ -1392,7 +1392,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1401,7 +1401,7 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1413,7 +1413,7 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>8476</v>
+        <v>8723</v>
       </c>
     </row>
     <row r="11">
@@ -1421,7 +1421,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1430,7 +1430,7 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1442,7 +1442,7 @@
         <v>3</v>
       </c>
       <c r="I11">
-        <v>8152</v>
+        <v>8405</v>
       </c>
     </row>
     <row r="12">
@@ -1450,7 +1450,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1459,7 +1459,7 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1471,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="I12">
-        <v>7759</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="13">
@@ -1479,7 +1479,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1500,7 +1500,7 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>7669</v>
+        <v>7897</v>
       </c>
     </row>
     <row r="14">
@@ -1508,7 +1508,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1517,7 +1517,7 @@
         <v>29</v>
       </c>
       <c r="E14">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1529,7 +1529,7 @@
         <v>3</v>
       </c>
       <c r="I14">
-        <v>7262</v>
+        <v>7512</v>
       </c>
     </row>
     <row r="15">
@@ -1537,7 +1537,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1546,7 +1546,7 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1558,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="I15">
-        <v>7081</v>
+        <v>7308</v>
       </c>
     </row>
     <row r="16">
@@ -1566,16 +1566,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E16">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1587,7 +1587,7 @@
         <v>3</v>
       </c>
       <c r="I16">
-        <v>6720</v>
+        <v>6943</v>
       </c>
     </row>
     <row r="17">
@@ -1595,7 +1595,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1604,7 +1604,7 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1616,7 +1616,7 @@
         <v>3</v>
       </c>
       <c r="I17">
-        <v>6592</v>
+        <v>6807</v>
       </c>
     </row>
     <row r="18">
@@ -1624,7 +1624,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1633,7 +1633,7 @@
         <v>18</v>
       </c>
       <c r="E18">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>6301</v>
+        <v>6508</v>
       </c>
     </row>
     <row r="19">
@@ -1653,7 +1653,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1662,7 +1662,7 @@
         <v>30</v>
       </c>
       <c r="E19">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1674,7 +1674,7 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>6119</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="20">
@@ -1682,7 +1682,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1691,7 +1691,7 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1703,7 +1703,7 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>6028</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="21">
@@ -1711,7 +1711,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1720,7 +1720,7 @@
         <v>20</v>
       </c>
       <c r="E21">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>5714</v>
+        <v>5875</v>
       </c>
     </row>
     <row r="22">
@@ -1740,7 +1740,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1749,7 +1749,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1761,7 +1761,7 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>5685</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="23">
@@ -1769,16 +1769,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1790,7 +1790,7 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>5332</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="24">
@@ -1798,7 +1798,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1807,7 +1807,7 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1819,7 +1819,7 @@
         <v>3</v>
       </c>
       <c r="I24">
-        <v>5303</v>
+        <v>5468</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -368,12 +368,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>min_visits</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>max_visits</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -383,22 +383,37 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>q1</t>
+          <t>q1_visits</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>median_visitst</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>q3</t>
+          <t>q3_visits</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>n_pts</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
@@ -407,28 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>4</v>
       </c>
       <c r="I2">
-        <v>18925</v>
+        <v>16978</v>
+      </c>
+      <c r="J2">
+        <v>0.02</v>
+      </c>
+      <c r="K2">
+        <v>2.48</v>
+      </c>
+      <c r="L2">
+        <v>2.56</v>
       </c>
     </row>
     <row r="3">
@@ -436,28 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.79</v>
+        <v>1.71</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>27</v>
       </c>
       <c r="E3">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
       <c r="I3">
-        <v>15445</v>
+        <v>16978</v>
+      </c>
+      <c r="J3">
+        <v>0.02</v>
+      </c>
+      <c r="K3">
+        <v>1.67</v>
+      </c>
+      <c r="L3">
+        <v>1.74</v>
       </c>
     </row>
     <row r="4">
@@ -465,28 +498,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.81</v>
+        <v>1.46</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="H4">
-        <v>4</v>
-      </c>
       <c r="I4">
-        <v>14088</v>
+        <v>16978</v>
+      </c>
+      <c r="J4">
+        <v>0.02</v>
+      </c>
+      <c r="K4">
+        <v>1.43</v>
+      </c>
+      <c r="L4">
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -494,28 +536,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.61</v>
+        <v>1.22</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
       <c r="I5">
-        <v>12614</v>
+        <v>16978</v>
+      </c>
+      <c r="J5">
+        <v>0.02</v>
+      </c>
+      <c r="K5">
+        <v>1.19</v>
+      </c>
+      <c r="L5">
+        <v>1.25</v>
       </c>
     </row>
     <row r="6">
@@ -523,28 +574,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.67</v>
+        <v>1.16</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>2.28</v>
+        <v>2.01</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>2</v>
       </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
       <c r="I6">
-        <v>11322</v>
+        <v>16978</v>
+      </c>
+      <c r="J6">
+        <v>0.02</v>
+      </c>
+      <c r="K6">
+        <v>1.13</v>
+      </c>
+      <c r="L6">
+        <v>1.19</v>
       </c>
     </row>
     <row r="7">
@@ -552,28 +612,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.61</v>
+        <v>1.06</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>28</v>
       </c>
       <c r="E7">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>10363</v>
+        <v>16978</v>
+      </c>
+      <c r="J7">
+        <v>0.01</v>
+      </c>
+      <c r="K7">
+        <v>1.03</v>
+      </c>
+      <c r="L7">
+        <v>1.09</v>
       </c>
     </row>
     <row r="8">
@@ -581,28 +650,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.64</v>
+        <v>1.02</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>31</v>
       </c>
       <c r="E8">
-        <v>2.23</v>
+        <v>1.89</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>9780</v>
+        <v>16978</v>
+      </c>
+      <c r="J8">
+        <v>0.01</v>
+      </c>
+      <c r="K8">
+        <v>0.99</v>
+      </c>
+      <c r="L8">
+        <v>1.04</v>
       </c>
     </row>
     <row r="9">
@@ -610,28 +688,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.54</v>
+        <v>0.92</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E9">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>9232</v>
+        <v>16978</v>
+      </c>
+      <c r="J9">
+        <v>0.01</v>
+      </c>
+      <c r="K9">
+        <v>0.89</v>
+      </c>
+      <c r="L9">
+        <v>0.95</v>
       </c>
     </row>
     <row r="10">
@@ -639,28 +726,37 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.6</v>
+        <v>0.91</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>8898</v>
+        <v>16978</v>
+      </c>
+      <c r="J10">
+        <v>0.01</v>
+      </c>
+      <c r="K10">
+        <v>0.89</v>
+      </c>
+      <c r="L10">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -668,28 +764,37 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.58</v>
+        <v>0.87</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E11">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>8566</v>
+        <v>16978</v>
+      </c>
+      <c r="J11">
+        <v>0.01</v>
+      </c>
+      <c r="K11">
+        <v>0.85</v>
+      </c>
+      <c r="L11">
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -697,28 +802,37 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.55</v>
+        <v>0.83</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>43</v>
       </c>
       <c r="E12">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>8131</v>
+        <v>16978</v>
+      </c>
+      <c r="J12">
+        <v>0.01</v>
+      </c>
+      <c r="K12">
+        <v>0.8</v>
+      </c>
+      <c r="L12">
+        <v>0.85</v>
       </c>
     </row>
     <row r="13">
@@ -726,28 +840,37 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.63</v>
+        <v>0.84</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>33</v>
       </c>
       <c r="E13">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>8056</v>
+        <v>16978</v>
+      </c>
+      <c r="J13">
+        <v>0.01</v>
+      </c>
+      <c r="K13">
+        <v>0.82</v>
+      </c>
+      <c r="L13">
+        <v>0.87</v>
       </c>
     </row>
     <row r="14">
@@ -755,28 +878,37 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.55</v>
+        <v>0.78</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E14">
-        <v>2.09</v>
+        <v>1.64</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>7628</v>
+        <v>16978</v>
+      </c>
+      <c r="J14">
+        <v>0.01</v>
+      </c>
+      <c r="K14">
+        <v>0.75</v>
+      </c>
+      <c r="L14">
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
@@ -784,28 +916,37 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2.59</v>
+        <v>0.76</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E15">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>7416</v>
+        <v>16978</v>
+      </c>
+      <c r="J15">
+        <v>0.01</v>
+      </c>
+      <c r="K15">
+        <v>0.74</v>
+      </c>
+      <c r="L15">
+        <v>0.79</v>
       </c>
     </row>
     <row r="16">
@@ -813,28 +954,37 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.58</v>
+        <v>0.72</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>23</v>
       </c>
       <c r="E16">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>7051</v>
+        <v>16978</v>
+      </c>
+      <c r="J16">
+        <v>0.01</v>
+      </c>
+      <c r="K16">
+        <v>0.7</v>
+      </c>
+      <c r="L16">
+        <v>0.75</v>
       </c>
     </row>
     <row r="17">
@@ -842,28 +992,37 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2.55</v>
+        <v>0.7</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17">
-        <v>2.13</v>
+        <v>1.59</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>6913</v>
+        <v>16978</v>
+      </c>
+      <c r="J17">
+        <v>0.01</v>
+      </c>
+      <c r="K17">
+        <v>0.68</v>
+      </c>
+      <c r="L17">
+        <v>0.73</v>
       </c>
     </row>
     <row r="18">
@@ -871,28 +1030,37 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2.52</v>
+        <v>0.67</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>6599</v>
+        <v>16978</v>
+      </c>
+      <c r="J18">
+        <v>0.01</v>
+      </c>
+      <c r="K18">
+        <v>0.64</v>
+      </c>
+      <c r="L18">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -900,28 +1068,37 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2.55</v>
+        <v>0.66</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E19">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>6429</v>
+        <v>16978</v>
+      </c>
+      <c r="J19">
+        <v>0.01</v>
+      </c>
+      <c r="K19">
+        <v>0.64</v>
+      </c>
+      <c r="L19">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -929,28 +1106,37 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2.56</v>
+        <v>0.64</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>25</v>
       </c>
       <c r="E20">
-        <v>2.13</v>
+        <v>1.53</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>6278</v>
+        <v>16978</v>
+      </c>
+      <c r="J20">
+        <v>0.01</v>
+      </c>
+      <c r="K20">
+        <v>0.62</v>
+      </c>
+      <c r="L20">
+        <v>0.66</v>
       </c>
     </row>
     <row r="21">
@@ -958,28 +1144,37 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2.52</v>
+        <v>0.59</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>20</v>
       </c>
       <c r="E21">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>5955</v>
+        <v>16978</v>
+      </c>
+      <c r="J21">
+        <v>0.01</v>
+      </c>
+      <c r="K21">
+        <v>0.57</v>
+      </c>
+      <c r="L21">
+        <v>0.62</v>
       </c>
     </row>
     <row r="22">
@@ -987,28 +1182,37 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.6</v>
+        <v>0.62</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>21</v>
       </c>
       <c r="E22">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>5929</v>
+        <v>16978</v>
+      </c>
+      <c r="J22">
+        <v>0.01</v>
+      </c>
+      <c r="K22">
+        <v>0.59</v>
+      </c>
+      <c r="L22">
+        <v>0.64</v>
       </c>
     </row>
     <row r="23">
@@ -1016,28 +1220,37 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>21</v>
       </c>
       <c r="E23">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>5565</v>
+        <v>16978</v>
+      </c>
+      <c r="J23">
+        <v>0.01</v>
+      </c>
+      <c r="K23">
+        <v>0.54</v>
+      </c>
+      <c r="L23">
+        <v>0.58</v>
       </c>
     </row>
     <row r="24">
@@ -1045,28 +1258,37 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.57</v>
+        <v>0.57</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>20</v>
       </c>
       <c r="E24">
-        <v>2.09</v>
+        <v>1.46</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>5525</v>
+        <v>16978</v>
+      </c>
+      <c r="J24">
+        <v>0.01</v>
+      </c>
+      <c r="K24">
+        <v>0.54</v>
+      </c>
+      <c r="L24">
+        <v>0.59</v>
       </c>
     </row>
     <row r="25">
@@ -1074,28 +1296,37 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2.52</v>
+        <v>0.51</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>20</v>
       </c>
       <c r="E25">
-        <v>2.08</v>
+        <v>1.38</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>5110</v>
+        <v>16978</v>
+      </c>
+      <c r="J25">
+        <v>0.01</v>
+      </c>
+      <c r="K25">
+        <v>0.49</v>
+      </c>
+      <c r="L25">
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1121,12 +1352,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>min_visits</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>max_visits</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1136,22 +1367,37 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>q1</t>
+          <t>q1_visits</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>median_visits</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>q3</t>
+          <t>q3_visits</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>n_pts</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
@@ -1160,28 +1406,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>4</v>
       </c>
       <c r="I2">
-        <v>18925</v>
+        <v>16978</v>
+      </c>
+      <c r="J2">
+        <v>0.02</v>
+      </c>
+      <c r="K2">
+        <v>2.48</v>
+      </c>
+      <c r="L2">
+        <v>2.56</v>
       </c>
     </row>
     <row r="3">
@@ -1189,28 +1444,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.79</v>
+        <v>1.77</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>27</v>
       </c>
       <c r="E3">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>15122</v>
+        <v>15934</v>
+      </c>
+      <c r="J3">
+        <v>0.02</v>
+      </c>
+      <c r="K3">
+        <v>1.73</v>
+      </c>
+      <c r="L3">
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
@@ -1218,28 +1482,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.81</v>
+        <v>1.67</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="H4">
-        <v>4</v>
-      </c>
       <c r="I4">
-        <v>13797</v>
+        <v>14690</v>
+      </c>
+      <c r="J4">
+        <v>0.02</v>
+      </c>
+      <c r="K4">
+        <v>1.63</v>
+      </c>
+      <c r="L4">
+        <v>1.71</v>
       </c>
     </row>
     <row r="5">
@@ -1247,28 +1520,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.68</v>
+        <v>1.47</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
       <c r="I5">
-        <v>11630</v>
+        <v>14067</v>
+      </c>
+      <c r="J5">
+        <v>0.02</v>
+      </c>
+      <c r="K5">
+        <v>1.43</v>
+      </c>
+      <c r="L5">
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
@@ -1276,28 +1558,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <v>2</v>
       </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
       <c r="I6">
-        <v>10819</v>
+        <v>13705</v>
+      </c>
+      <c r="J6">
+        <v>0.02</v>
+      </c>
+      <c r="K6">
+        <v>1.4</v>
+      </c>
+      <c r="L6">
+        <v>1.47</v>
       </c>
     </row>
     <row r="7">
@@ -1305,28 +1596,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.62</v>
+        <v>1.34</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>28</v>
       </c>
       <c r="E7">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>2</v>
       </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
       <c r="I7">
-        <v>10035</v>
+        <v>13405</v>
+      </c>
+      <c r="J7">
+        <v>0.02</v>
+      </c>
+      <c r="K7">
+        <v>1.31</v>
+      </c>
+      <c r="L7">
+        <v>1.38</v>
       </c>
     </row>
     <row r="8">
@@ -1334,28 +1634,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.64</v>
+        <v>1.31</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>31</v>
       </c>
       <c r="E8">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>2</v>
       </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
       <c r="I8">
-        <v>9539</v>
+        <v>13143</v>
+      </c>
+      <c r="J8">
+        <v>0.02</v>
+      </c>
+      <c r="K8">
+        <v>1.27</v>
+      </c>
+      <c r="L8">
+        <v>1.34</v>
       </c>
     </row>
     <row r="9">
@@ -1363,28 +1672,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.54</v>
+        <v>1.21</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E9">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>2</v>
       </c>
-      <c r="H9">
-        <v>3</v>
-      </c>
       <c r="I9">
-        <v>9022</v>
+        <v>12915</v>
+      </c>
+      <c r="J9">
+        <v>0.02</v>
+      </c>
+      <c r="K9">
+        <v>1.18</v>
+      </c>
+      <c r="L9">
+        <v>1.24</v>
       </c>
     </row>
     <row r="10">
@@ -1392,28 +1710,37 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.6</v>
+        <v>1.22</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>2</v>
       </c>
-      <c r="H10">
-        <v>3</v>
-      </c>
       <c r="I10">
-        <v>8723</v>
+        <v>12726</v>
+      </c>
+      <c r="J10">
+        <v>0.02</v>
+      </c>
+      <c r="K10">
+        <v>1.18</v>
+      </c>
+      <c r="L10">
+        <v>1.25</v>
       </c>
     </row>
     <row r="11">
@@ -1421,28 +1748,37 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.58</v>
+        <v>1.18</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E11">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>2</v>
       </c>
-      <c r="H11">
-        <v>3</v>
-      </c>
       <c r="I11">
-        <v>8405</v>
+        <v>12555</v>
+      </c>
+      <c r="J11">
+        <v>0.02</v>
+      </c>
+      <c r="K11">
+        <v>1.15</v>
+      </c>
+      <c r="L11">
+        <v>1.21</v>
       </c>
     </row>
     <row r="12">
@@ -1450,28 +1786,37 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.56</v>
+        <v>1.13</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>43</v>
       </c>
       <c r="E12">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>2</v>
       </c>
-      <c r="H12">
-        <v>3</v>
-      </c>
       <c r="I12">
-        <v>8011</v>
+        <v>12414</v>
+      </c>
+      <c r="J12">
+        <v>0.02</v>
+      </c>
+      <c r="K12">
+        <v>1.1</v>
+      </c>
+      <c r="L12">
+        <v>1.17</v>
       </c>
     </row>
     <row r="13">
@@ -1479,28 +1824,37 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.64</v>
+        <v>1.16</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>33</v>
       </c>
       <c r="E13">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>2</v>
       </c>
-      <c r="H13">
-        <v>3</v>
-      </c>
       <c r="I13">
-        <v>7897</v>
+        <v>12275</v>
+      </c>
+      <c r="J13">
+        <v>0.02</v>
+      </c>
+      <c r="K13">
+        <v>1.13</v>
+      </c>
+      <c r="L13">
+        <v>1.2</v>
       </c>
     </row>
     <row r="14">
@@ -1508,28 +1862,37 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.54</v>
+        <v>1.09</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E14">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>2</v>
       </c>
-      <c r="H14">
-        <v>3</v>
-      </c>
       <c r="I14">
-        <v>7512</v>
+        <v>12101</v>
+      </c>
+      <c r="J14">
+        <v>0.02</v>
+      </c>
+      <c r="K14">
+        <v>1.06</v>
+      </c>
+      <c r="L14">
+        <v>1.13</v>
       </c>
     </row>
     <row r="15">
@@ -1537,28 +1900,37 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2.59</v>
+        <v>1.08</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E15">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>7308</v>
+        <v>11975</v>
+      </c>
+      <c r="J15">
+        <v>0.02</v>
+      </c>
+      <c r="K15">
+        <v>1.05</v>
+      </c>
+      <c r="L15">
+        <v>1.12</v>
       </c>
     </row>
     <row r="16">
@@ -1566,28 +1938,37 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>23</v>
       </c>
       <c r="E16">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>6943</v>
+        <v>11843</v>
+      </c>
+      <c r="J16">
+        <v>0.02</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1.07</v>
       </c>
     </row>
     <row r="17">
@@ -1595,28 +1976,37 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2.56</v>
+        <v>1.02</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>6807</v>
+        <v>11724</v>
+      </c>
+      <c r="J17">
+        <v>0.02</v>
+      </c>
+      <c r="K17">
+        <v>0.98</v>
+      </c>
+      <c r="L17">
+        <v>1.05</v>
       </c>
     </row>
     <row r="18">
@@ -1624,28 +2014,37 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2.52</v>
+        <v>0.97</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>6508</v>
+        <v>11598</v>
+      </c>
+      <c r="J18">
+        <v>0.02</v>
+      </c>
+      <c r="K18">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
       </c>
     </row>
     <row r="19">
@@ -1653,28 +2052,37 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2.55</v>
+        <v>0.98</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E19">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>6334</v>
+        <v>11478</v>
+      </c>
+      <c r="J19">
+        <v>0.02</v>
+      </c>
+      <c r="K19">
+        <v>0.95</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
       </c>
     </row>
     <row r="20">
@@ -1682,28 +2090,37 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2.56</v>
+        <v>0.95</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>25</v>
       </c>
       <c r="E20">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>6204</v>
+        <v>11364</v>
+      </c>
+      <c r="J20">
+        <v>0.02</v>
+      </c>
+      <c r="K20">
+        <v>0.92</v>
+      </c>
+      <c r="L20">
+        <v>0.99</v>
       </c>
     </row>
     <row r="21">
@@ -1711,28 +2128,37 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2.51</v>
+        <v>0.9</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>20</v>
       </c>
       <c r="E21">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>5875</v>
+        <v>11251</v>
+      </c>
+      <c r="J21">
+        <v>0.02</v>
+      </c>
+      <c r="K21">
+        <v>0.87</v>
+      </c>
+      <c r="L21">
+        <v>0.93</v>
       </c>
     </row>
     <row r="22">
@@ -1740,28 +2166,37 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.6</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>21</v>
       </c>
       <c r="E22">
-        <v>2.17</v>
+        <v>1.81</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>5847</v>
+        <v>11131</v>
+      </c>
+      <c r="J22">
+        <v>0.02</v>
+      </c>
+      <c r="K22">
+        <v>0.91</v>
+      </c>
+      <c r="L22">
+        <v>0.97</v>
       </c>
     </row>
     <row r="23">
@@ -1769,28 +2204,37 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2.52</v>
+        <v>0.86</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>21</v>
       </c>
       <c r="E23">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>5490</v>
+        <v>10994</v>
+      </c>
+      <c r="J23">
+        <v>0.02</v>
+      </c>
+      <c r="K23">
+        <v>0.83</v>
+      </c>
+      <c r="L23">
+        <v>0.89</v>
       </c>
     </row>
     <row r="24">
@@ -1798,28 +2242,75 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.57</v>
+        <v>0.88</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>20</v>
       </c>
       <c r="E24">
-        <v>2.09</v>
+        <v>1.74</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>5468</v>
+        <v>10883</v>
+      </c>
+      <c r="J24">
+        <v>0.02</v>
+      </c>
+      <c r="K24">
+        <v>0.85</v>
+      </c>
+      <c r="L24">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>0.83</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>20.37</v>
+      </c>
+      <c r="E25">
+        <v>1.7</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1.02</v>
+      </c>
+      <c r="I25">
+        <v>10763</v>
+      </c>
+      <c r="J25">
+        <v>0.02</v>
+      </c>
+      <c r="K25">
+        <v>0.79</v>
+      </c>
+      <c r="L25">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
@@ -422,16 +422,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -443,16 +443,16 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J2">
         <v>0.02</v>
       </c>
       <c r="K2">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="L2">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -469,7 +469,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -478,19 +478,19 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J3">
         <v>0.02</v>
       </c>
       <c r="K3">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="L3">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="4">
@@ -498,16 +498,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -519,16 +519,16 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J4">
         <v>0.02</v>
       </c>
       <c r="K4">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="L4">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="5">
@@ -536,37 +536,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J5">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K5">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="L5">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="6">
@@ -574,7 +574,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -583,7 +583,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -595,16 +595,16 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J6">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K6">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="L6">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="7">
@@ -612,7 +612,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -630,19 +630,19 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J7">
         <v>0.01</v>
       </c>
       <c r="K7">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="L7">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="8">
@@ -650,7 +650,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -671,16 +671,16 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J8">
         <v>0.01</v>
       </c>
       <c r="K8">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="L8">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="9">
@@ -688,16 +688,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E9">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -709,16 +709,16 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J9">
         <v>0.01</v>
       </c>
       <c r="K9">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="L9">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="10">
@@ -726,16 +726,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -747,16 +747,16 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J10">
         <v>0.01</v>
       </c>
       <c r="K10">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="L10">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -764,16 +764,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -785,16 +785,16 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J11">
         <v>0.01</v>
       </c>
       <c r="K11">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="L11">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="12">
@@ -802,7 +802,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -811,7 +811,7 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -823,16 +823,16 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J12">
         <v>0.01</v>
       </c>
       <c r="K12">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="L12">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13">
@@ -840,7 +840,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -849,7 +849,7 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -861,16 +861,16 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J13">
         <v>0.01</v>
       </c>
       <c r="K13">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="L13">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="14">
@@ -878,16 +878,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E14">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J14">
         <v>0.01</v>
       </c>
       <c r="K14">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L14">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="15">
@@ -916,16 +916,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E15">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J15">
         <v>0.01</v>
       </c>
       <c r="K15">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="L15">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="16">
@@ -954,7 +954,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>23</v>
       </c>
       <c r="E16">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J16">
         <v>0.01</v>
       </c>
       <c r="K16">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L16">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17">
@@ -992,7 +992,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1013,16 +1013,16 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J17">
         <v>0.01</v>
       </c>
       <c r="K17">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="L17">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="18">
@@ -1030,7 +1030,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>17</v>
       </c>
       <c r="E18">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1051,16 +1051,16 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J18">
         <v>0.01</v>
       </c>
       <c r="K18">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L18">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="19">
@@ -1068,7 +1068,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>21</v>
       </c>
       <c r="E19">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1089,16 +1089,16 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J19">
         <v>0.01</v>
       </c>
       <c r="K19">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="L19">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="20">
@@ -1106,7 +1106,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J20">
         <v>0.01</v>
       </c>
       <c r="K20">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="L20">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>20</v>
       </c>
       <c r="E21">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1162,19 +1162,19 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J21">
         <v>0.01</v>
       </c>
       <c r="K21">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="L21">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="22">
@@ -1182,7 +1182,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1200,19 +1200,19 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J22">
         <v>0.01</v>
       </c>
       <c r="K22">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="L22">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="23">
@@ -1220,7 +1220,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1229,7 +1229,7 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J23">
         <v>0.01</v>
       </c>
       <c r="K23">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="L23">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="24">
@@ -1258,7 +1258,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1279,16 +1279,16 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J24">
         <v>0.01</v>
       </c>
       <c r="K24">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="L24">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="25">
@@ -1296,7 +1296,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>20</v>
       </c>
       <c r="E25">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1317,16 +1317,16 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J25">
         <v>0.01</v>
       </c>
       <c r="K25">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="L25">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -1406,16 +1406,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J2">
         <v>0.02</v>
       </c>
       <c r="K2">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="L2">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="3">
@@ -1444,7 +1444,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1465,16 +1465,16 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>15934</v>
+        <v>21794</v>
       </c>
       <c r="J3">
         <v>0.02</v>
       </c>
       <c r="K3">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="L3">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="4">
@@ -1482,16 +1482,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1500,19 +1500,19 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>14690</v>
+        <v>20883</v>
       </c>
       <c r="J4">
         <v>0.02</v>
       </c>
       <c r="K4">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="L4">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="5">
@@ -1520,16 +1520,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1541,16 +1541,16 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>14067</v>
+        <v>19547</v>
       </c>
       <c r="J5">
         <v>0.02</v>
       </c>
       <c r="K5">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="L5">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="6">
@@ -1558,7 +1558,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1567,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1579,16 +1579,16 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>13705</v>
+        <v>18393</v>
       </c>
       <c r="J6">
         <v>0.02</v>
       </c>
       <c r="K6">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="L6">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="7">
@@ -1596,7 +1596,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1605,7 +1605,7 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1617,16 +1617,16 @@
         <v>2</v>
       </c>
       <c r="I7">
-        <v>13405</v>
+        <v>17568</v>
       </c>
       <c r="J7">
         <v>0.02</v>
       </c>
       <c r="K7">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="L7">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="8">
@@ -1634,7 +1634,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1643,28 +1643,28 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8">
-        <v>13143</v>
+        <v>16901</v>
       </c>
       <c r="J8">
         <v>0.02</v>
       </c>
       <c r="K8">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="L8">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="9">
@@ -1672,37 +1672,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E9">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>2</v>
       </c>
       <c r="I9">
-        <v>12915</v>
+        <v>16300</v>
       </c>
       <c r="J9">
         <v>0.02</v>
       </c>
       <c r="K9">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="L9">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="10">
@@ -1710,37 +1710,37 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>2</v>
       </c>
       <c r="I10">
-        <v>12726</v>
+        <v>15771</v>
       </c>
       <c r="J10">
         <v>0.02</v>
       </c>
       <c r="K10">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="L10">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="11">
@@ -1748,37 +1748,37 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>2</v>
       </c>
       <c r="I11">
-        <v>12555</v>
+        <v>15227</v>
       </c>
       <c r="J11">
         <v>0.02</v>
       </c>
       <c r="K11">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="L11">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -1786,7 +1786,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1795,28 +1795,28 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12">
-        <v>12414</v>
+        <v>14773</v>
       </c>
       <c r="J12">
         <v>0.02</v>
       </c>
       <c r="K12">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="L12">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1824,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1833,28 +1833,28 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="I13">
-        <v>12275</v>
+        <v>14336</v>
       </c>
       <c r="J13">
         <v>0.02</v>
       </c>
       <c r="K13">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="L13">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="14">
@@ -1862,37 +1862,37 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E14">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>2</v>
       </c>
       <c r="I14">
-        <v>12101</v>
+        <v>13859</v>
       </c>
       <c r="J14">
         <v>0.02</v>
       </c>
       <c r="K14">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="L14">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="15">
@@ -1900,37 +1900,37 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>21.67</v>
       </c>
       <c r="E15">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>11975</v>
+        <v>13467</v>
       </c>
       <c r="J15">
         <v>0.02</v>
       </c>
       <c r="K15">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="L15">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="16">
@@ -1938,7 +1938,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1947,28 +1947,28 @@
         <v>23</v>
       </c>
       <c r="E16">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>11843</v>
+        <v>13057</v>
       </c>
       <c r="J16">
         <v>0.02</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="L16">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="17">
@@ -1976,37 +1976,37 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>20.36</v>
       </c>
       <c r="E17">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>11724</v>
+        <v>12641</v>
       </c>
       <c r="J17">
         <v>0.02</v>
       </c>
       <c r="K17">
-        <v>0.98</v>
+        <v>1.28</v>
       </c>
       <c r="L17">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="18">
@@ -2014,7 +2014,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.97</v>
+        <v>1.29</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -2023,28 +2023,28 @@
         <v>17</v>
       </c>
       <c r="E18">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>11598</v>
+        <v>12240</v>
       </c>
       <c r="J18">
         <v>0.02</v>
       </c>
       <c r="K18">
-        <v>0.9399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="19">
@@ -2052,7 +2052,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.98</v>
+        <v>1.3</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2061,28 +2061,28 @@
         <v>21</v>
       </c>
       <c r="E19">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>11478</v>
+        <v>11888</v>
       </c>
       <c r="J19">
         <v>0.02</v>
       </c>
       <c r="K19">
-        <v>0.95</v>
+        <v>1.26</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="20">
@@ -2090,7 +2090,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.95</v>
+        <v>1.32</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -2099,28 +2099,28 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>11364</v>
+        <v>11544</v>
       </c>
       <c r="J20">
         <v>0.02</v>
       </c>
       <c r="K20">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="L20">
-        <v>0.99</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="21">
@@ -2128,7 +2128,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         <v>20</v>
       </c>
       <c r="E21">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2146,19 +2146,19 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>11251</v>
+        <v>11196</v>
       </c>
       <c r="J21">
         <v>0.02</v>
       </c>
       <c r="K21">
-        <v>0.87</v>
+        <v>1.23</v>
       </c>
       <c r="L21">
-        <v>0.93</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="22">
@@ -2166,7 +2166,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.9399999999999999</v>
+        <v>1.34</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2175,28 +2175,28 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>11131</v>
+        <v>10839</v>
       </c>
       <c r="J22">
         <v>0.02</v>
       </c>
       <c r="K22">
-        <v>0.91</v>
+        <v>1.3</v>
       </c>
       <c r="L22">
-        <v>0.97</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="23">
@@ -2204,7 +2204,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.86</v>
+        <v>1.26</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2222,19 +2222,19 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>10994</v>
+        <v>10485</v>
       </c>
       <c r="J23">
         <v>0.02</v>
       </c>
       <c r="K23">
-        <v>0.83</v>
+        <v>1.22</v>
       </c>
       <c r="L23">
-        <v>0.89</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="24">
@@ -2242,7 +2242,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.88</v>
+        <v>1.32</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>10883</v>
+        <v>10138</v>
       </c>
       <c r="J24">
         <v>0.02</v>
       </c>
       <c r="K24">
-        <v>0.85</v>
+        <v>1.28</v>
       </c>
       <c r="L24">
-        <v>0.92</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="25">
@@ -2280,7 +2280,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.83</v>
+        <v>1.26</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -2289,7 +2289,7 @@
         <v>20.37</v>
       </c>
       <c r="E25">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2298,19 +2298,19 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="I25">
-        <v>10763</v>
+        <v>9825</v>
       </c>
       <c r="J25">
         <v>0.02</v>
       </c>
       <c r="K25">
-        <v>0.79</v>
+        <v>1.22</v>
       </c>
       <c r="L25">
-        <v>0.86</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_monthly_visits_OMOP.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.67</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>231</v>
       </c>
       <c r="E2">
-        <v>2.67</v>
+        <v>12.42</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="K2">
-        <v>2.64</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="L2">
-        <v>2.71</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.86</v>
+        <v>6.75</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>202</v>
       </c>
       <c r="E3">
-        <v>2.31</v>
+        <v>11.05</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J3">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K3">
-        <v>1.83</v>
+        <v>6.61</v>
       </c>
       <c r="L3">
-        <v>1.89</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4">
@@ -498,37 +498,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.69</v>
+        <v>6.41</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>234</v>
       </c>
       <c r="E4">
-        <v>2.3</v>
+        <v>11.52</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J4">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="K4">
-        <v>1.66</v>
+        <v>6.26</v>
       </c>
       <c r="L4">
-        <v>1.72</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="5">
@@ -536,37 +536,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.4</v>
+        <v>5.37</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>208</v>
       </c>
       <c r="E5">
-        <v>2.05</v>
+        <v>10.31</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J5">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K5">
-        <v>1.38</v>
+        <v>5.24</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="6">
@@ -574,16 +574,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.28</v>
+        <v>4.99</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>742</v>
       </c>
       <c r="E6">
-        <v>2.06</v>
+        <v>11.45</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -592,19 +592,19 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J6">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="K6">
-        <v>1.26</v>
+        <v>4.84</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="7">
@@ -612,16 +612,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.15</v>
+        <v>4.38</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="E7">
-        <v>1.94</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -630,19 +630,19 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J7">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K7">
-        <v>1.12</v>
+        <v>4.25</v>
       </c>
       <c r="L7">
-        <v>1.17</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +650,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.1</v>
+        <v>4.22</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>285</v>
       </c>
       <c r="E8">
-        <v>1.94</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -668,19 +668,19 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J8">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="K8">
-        <v>1.07</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
-        <v>1.12</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="9">
@@ -688,16 +688,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.99</v>
+        <v>3.95</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>165</v>
       </c>
       <c r="E9">
-        <v>1.81</v>
+        <v>9.59</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -706,19 +706,19 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J9">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="K9">
-        <v>0.97</v>
+        <v>3.82</v>
       </c>
       <c r="L9">
-        <v>1.02</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="10">
@@ -726,16 +726,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.98</v>
+        <v>3.84</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>187</v>
       </c>
       <c r="E10">
-        <v>1.83</v>
+        <v>9.41</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -744,19 +744,19 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J10">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="K10">
-        <v>0.95</v>
+        <v>3.72</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="11">
@@ -764,16 +764,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.93</v>
+        <v>3.7</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>235</v>
       </c>
       <c r="E11">
-        <v>1.76</v>
+        <v>9.27</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -782,19 +782,19 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J11">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="K11">
-        <v>0.91</v>
+        <v>3.57</v>
       </c>
       <c r="L11">
-        <v>0.96</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="12">
@@ -802,16 +802,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.88</v>
+        <v>3.51</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>43</v>
+        <v>344</v>
       </c>
       <c r="E12">
-        <v>1.74</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -820,19 +820,19 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J12">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="K12">
-        <v>0.86</v>
+        <v>3.39</v>
       </c>
       <c r="L12">
-        <v>0.9</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="13">
@@ -840,16 +840,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.9</v>
+        <v>3.57</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>224</v>
       </c>
       <c r="E13">
-        <v>1.79</v>
+        <v>9.42</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -858,19 +858,19 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J13">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="K13">
-        <v>0.88</v>
+        <v>3.45</v>
       </c>
       <c r="L13">
-        <v>0.92</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="14">
@@ -878,16 +878,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.83</v>
+        <v>3.3</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="E14">
-        <v>1.69</v>
+        <v>8.91</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -896,19 +896,19 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J14">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="K14">
-        <v>0.8100000000000001</v>
+        <v>3.19</v>
       </c>
       <c r="L14">
-        <v>0.85</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="15">
@@ -916,16 +916,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.82</v>
+        <v>3.23</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="E15">
-        <v>1.7</v>
+        <v>8.76</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -934,19 +934,19 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J15">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="K15">
-        <v>0.8</v>
+        <v>3.12</v>
       </c>
       <c r="L15">
-        <v>0.84</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
@@ -954,16 +954,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.77</v>
+        <v>3.05</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>235</v>
       </c>
       <c r="E16">
-        <v>1.67</v>
+        <v>8.65</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -972,19 +972,19 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J16">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="K16">
-        <v>0.75</v>
+        <v>2.94</v>
       </c>
       <c r="L16">
-        <v>0.8</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="17">
@@ -992,16 +992,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.75</v>
+        <v>2.97</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>346</v>
       </c>
       <c r="E17">
-        <v>1.63</v>
+        <v>8.57</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1010,19 +1010,19 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J17">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="K17">
-        <v>0.73</v>
+        <v>2.85</v>
       </c>
       <c r="L17">
-        <v>0.77</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="18">
@@ -1030,16 +1030,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.71</v>
+        <v>2.86</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>17</v>
+        <v>284</v>
       </c>
       <c r="E18">
-        <v>1.55</v>
+        <v>8.49</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1048,19 +1048,19 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J18">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="K18">
-        <v>0.6899999999999999</v>
+        <v>2.75</v>
       </c>
       <c r="L18">
-        <v>0.73</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="19">
@@ -1068,16 +1068,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="E19">
-        <v>1.6</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1086,19 +1086,19 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J19">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K19">
-        <v>0.67</v>
+        <v>2.69</v>
       </c>
       <c r="L19">
-        <v>0.72</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="20">
@@ -1106,16 +1106,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.6899999999999999</v>
+        <v>2.75</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="E20">
-        <v>1.58</v>
+        <v>8.15</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J20">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K20">
-        <v>0.66</v>
+        <v>2.64</v>
       </c>
       <c r="L20">
-        <v>0.71</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="21">
@@ -1144,16 +1144,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.64</v>
+        <v>2.55</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="E21">
-        <v>1.52</v>
+        <v>7.87</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1165,16 +1165,16 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J21">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K21">
-        <v>0.62</v>
+        <v>2.44</v>
       </c>
       <c r="L21">
-        <v>0.66</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="22">
@@ -1182,16 +1182,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.65</v>
+        <v>2.61</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="E22">
-        <v>1.57</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1203,16 +1203,16 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J22">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K22">
-        <v>0.63</v>
+        <v>2.5</v>
       </c>
       <c r="L22">
-        <v>0.67</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="23">
@@ -1220,16 +1220,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.59</v>
+        <v>2.43</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="E23">
-        <v>1.46</v>
+        <v>7.94</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J23">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K23">
-        <v>0.57</v>
+        <v>2.32</v>
       </c>
       <c r="L23">
-        <v>0.61</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="24">
@@ -1258,16 +1258,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.6</v>
+        <v>2.43</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="E24">
-        <v>1.49</v>
+        <v>7.65</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1279,16 +1279,16 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J24">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K24">
-        <v>0.58</v>
+        <v>2.32</v>
       </c>
       <c r="L24">
-        <v>0.62</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="25">
@@ -1296,16 +1296,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.55</v>
+        <v>2.21</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="E25">
-        <v>1.42</v>
+        <v>7.43</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1317,16 +1317,16 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J25">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K25">
-        <v>0.53</v>
+        <v>2.11</v>
       </c>
       <c r="L25">
-        <v>0.57</v>
+        <v>2.31</v>
       </c>
     </row>
   </sheetData>
@@ -1406,37 +1406,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.67</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>231</v>
       </c>
       <c r="E2">
-        <v>2.67</v>
+        <v>12.42</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="K2">
-        <v>2.64</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="L2">
-        <v>2.71</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="3">
@@ -1444,37 +1444,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.89</v>
+        <v>6.89</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>202</v>
       </c>
       <c r="E3">
-        <v>2.34</v>
+        <v>11.24</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>21794</v>
+        <v>21815</v>
       </c>
       <c r="J3">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="K3">
-        <v>1.86</v>
+        <v>6.74</v>
       </c>
       <c r="L3">
-        <v>1.93</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="4">
@@ -1482,37 +1482,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.8</v>
+        <v>6.81</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>234</v>
       </c>
       <c r="E4">
-        <v>2.35</v>
+        <v>11.82</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>20883</v>
+        <v>20900</v>
       </c>
       <c r="J4">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="K4">
-        <v>1.77</v>
+        <v>6.65</v>
       </c>
       <c r="L4">
-        <v>1.83</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="5">
@@ -1520,37 +1520,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.58</v>
+        <v>6.03</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>208</v>
       </c>
       <c r="E5">
-        <v>2.15</v>
+        <v>10.9</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>19547</v>
+        <v>19555</v>
       </c>
       <c r="J5">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="K5">
-        <v>1.55</v>
+        <v>5.88</v>
       </c>
       <c r="L5">
-        <v>1.61</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="6">
@@ -1558,37 +1558,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.55</v>
+        <v>6.05</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>1310.12</v>
       </c>
       <c r="E6">
-        <v>2.2</v>
+        <v>14.78</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>18393</v>
+        <v>18398</v>
       </c>
       <c r="J6">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="K6">
-        <v>1.52</v>
+        <v>5.84</v>
       </c>
       <c r="L6">
-        <v>1.58</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="7">
@@ -1596,37 +1596,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.45</v>
+        <v>5.56</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>356.42</v>
       </c>
       <c r="E7">
-        <v>2.1</v>
+        <v>11.04</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>17568</v>
+        <v>17573</v>
       </c>
       <c r="J7">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="K7">
-        <v>1.42</v>
+        <v>5.39</v>
       </c>
       <c r="L7">
-        <v>1.48</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="8">
@@ -1634,37 +1634,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.44</v>
+        <v>5.58</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>285</v>
       </c>
       <c r="E8">
-        <v>2.12</v>
+        <v>10.84</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>16901</v>
+        <v>16906</v>
       </c>
       <c r="J8">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="K8">
-        <v>1.41</v>
+        <v>5.41</v>
       </c>
       <c r="L8">
-        <v>1.48</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="9">
@@ -1672,16 +1672,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.36</v>
+        <v>5.38</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>165</v>
       </c>
       <c r="E9">
-        <v>2.01</v>
+        <v>10.88</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1690,19 +1690,19 @@
         <v>1</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>16300</v>
+        <v>16305</v>
       </c>
       <c r="J9">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="K9">
-        <v>1.33</v>
+        <v>5.22</v>
       </c>
       <c r="L9">
-        <v>1.39</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="10">
@@ -1710,16 +1710,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1.38</v>
+        <v>5.42</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>187</v>
       </c>
       <c r="E10">
-        <v>2.05</v>
+        <v>10.85</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1728,19 +1728,19 @@
         <v>1</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>15771</v>
+        <v>15776</v>
       </c>
       <c r="J10">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="K10">
-        <v>1.35</v>
+        <v>5.25</v>
       </c>
       <c r="L10">
-        <v>1.41</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="11">
@@ -1748,16 +1748,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.36</v>
+        <v>5.4</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>235</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>10.82</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1766,19 +1766,19 @@
         <v>1</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>15227</v>
+        <v>15232</v>
       </c>
       <c r="J11">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="K11">
-        <v>1.33</v>
+        <v>5.23</v>
       </c>
       <c r="L11">
-        <v>1.4</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="12">
@@ -1786,16 +1786,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1.33</v>
+        <v>5.29</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>43</v>
+        <v>344</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>10.88</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1804,19 +1804,19 @@
         <v>1</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>14773</v>
+        <v>14778</v>
       </c>
       <c r="J12">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="K12">
-        <v>1.29</v>
+        <v>5.11</v>
       </c>
       <c r="L12">
-        <v>1.36</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="13">
@@ -1824,16 +1824,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.4</v>
+        <v>5.55</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>224</v>
       </c>
       <c r="E13">
-        <v>2.08</v>
+        <v>11.32</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1842,19 +1842,19 @@
         <v>1</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>14336</v>
+        <v>14340</v>
       </c>
       <c r="J13">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="K13">
-        <v>1.36</v>
+        <v>5.37</v>
       </c>
       <c r="L13">
-        <v>1.43</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="14">
@@ -1862,16 +1862,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.34</v>
+        <v>5.31</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="E14">
-        <v>1.99</v>
+        <v>10.87</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1880,19 +1880,19 @@
         <v>1</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>13859</v>
+        <v>13862</v>
       </c>
       <c r="J14">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="K14">
-        <v>1.3</v>
+        <v>5.13</v>
       </c>
       <c r="L14">
-        <v>1.37</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="15">
@@ -1900,16 +1900,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1.35</v>
+        <v>5.35</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>21.67</v>
+        <v>174</v>
       </c>
       <c r="E15">
-        <v>2.03</v>
+        <v>10.79</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1918,19 +1918,19 @@
         <v>1</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>13467</v>
+        <v>13470</v>
       </c>
       <c r="J15">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="K15">
-        <v>1.32</v>
+        <v>5.17</v>
       </c>
       <c r="L15">
-        <v>1.39</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="16">
@@ -1938,16 +1938,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1.32</v>
+        <v>5.2</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>235</v>
       </c>
       <c r="E16">
-        <v>2.02</v>
+        <v>10.8</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1956,19 +1956,19 @@
         <v>1</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>13057</v>
+        <v>13060</v>
       </c>
       <c r="J16">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="K16">
-        <v>1.28</v>
+        <v>5.02</v>
       </c>
       <c r="L16">
-        <v>1.35</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="17">
@@ -1976,16 +1976,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1.32</v>
+        <v>5.22</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>20.36</v>
+        <v>346</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>10.88</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1994,19 +1994,19 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>12641</v>
+        <v>12644</v>
       </c>
       <c r="J17">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K17">
-        <v>1.28</v>
+        <v>5.03</v>
       </c>
       <c r="L17">
-        <v>1.35</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="18">
@@ -2014,16 +2014,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.29</v>
+        <v>5.22</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>17</v>
+        <v>284</v>
       </c>
       <c r="E18">
-        <v>1.91</v>
+        <v>11</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2032,19 +2032,19 @@
         <v>1</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>12240</v>
+        <v>12243</v>
       </c>
       <c r="J18">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K18">
-        <v>1.25</v>
+        <v>5.02</v>
       </c>
       <c r="L18">
-        <v>1.32</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="19">
@@ -2052,16 +2052,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1.3</v>
+        <v>5.23</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>10.65</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2070,19 +2070,19 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>11888</v>
+        <v>11891</v>
       </c>
       <c r="J19">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K19">
-        <v>1.26</v>
+        <v>5.04</v>
       </c>
       <c r="L19">
-        <v>1.34</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="20">
@@ -2090,16 +2090,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1.32</v>
+        <v>5.31</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>10.74</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -2108,19 +2108,19 @@
         <v>1</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>11544</v>
+        <v>11546</v>
       </c>
       <c r="J20">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K20">
-        <v>1.29</v>
+        <v>5.11</v>
       </c>
       <c r="L20">
-        <v>1.36</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="21">
@@ -2128,37 +2128,37 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1.27</v>
+        <v>5.07</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="E21">
-        <v>1.96</v>
+        <v>10.59</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I21">
-        <v>11196</v>
+        <v>11198</v>
       </c>
       <c r="J21">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K21">
-        <v>1.23</v>
+        <v>4.87</v>
       </c>
       <c r="L21">
-        <v>1.3</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="22">
@@ -2166,16 +2166,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>1.34</v>
+        <v>5.36</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="E22">
-        <v>2.05</v>
+        <v>10.93</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2184,19 +2184,19 @@
         <v>1</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>10839</v>
+        <v>10841</v>
       </c>
       <c r="J22">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="K22">
-        <v>1.3</v>
+        <v>5.16</v>
       </c>
       <c r="L22">
-        <v>1.38</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="23">
@@ -2204,37 +2204,37 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>1.26</v>
+        <v>5.14</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="E23">
-        <v>1.94</v>
+        <v>10.86</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I23">
-        <v>10485</v>
+        <v>10487</v>
       </c>
       <c r="J23">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="K23">
-        <v>1.22</v>
+        <v>4.93</v>
       </c>
       <c r="L23">
-        <v>1.3</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="24">
@@ -2242,16 +2242,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1.32</v>
+        <v>5.32</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>10.65</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2260,19 +2260,19 @@
         <v>1</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>10138</v>
+        <v>10140</v>
       </c>
       <c r="J24">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="K24">
-        <v>1.28</v>
+        <v>5.12</v>
       </c>
       <c r="L24">
-        <v>1.36</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="25">
@@ -2280,16 +2280,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>1.26</v>
+        <v>5.11</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>20.37</v>
+        <v>180.32</v>
       </c>
       <c r="E25">
-        <v>1.98</v>
+        <v>10.78</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2298,19 +2298,19 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>2.04</v>
+        <v>6.11</v>
       </c>
       <c r="I25">
-        <v>9825</v>
+        <v>9827</v>
       </c>
       <c r="J25">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="K25">
-        <v>1.22</v>
+        <v>4.89</v>
       </c>
       <c r="L25">
-        <v>1.3</v>
+        <v>5.32</v>
       </c>
     </row>
   </sheetData>
